--- a/docs/master_plan.xlsx
+++ b/docs/master_plan.xlsx
@@ -76,7 +76,7 @@
     <t>Kiến trúc</t>
   </si>
   <si>
-    <t>Khởi tạo project .NET 8 Web API, cấu trúc layer Controller/Service/Repository</t>
+    <t>Khởi tạo project FastAPI (Python 3.12), cấu trúc layer Router/Service/Repository</t>
   </si>
   <si>
     <t>Must</t>
@@ -94,7 +94,7 @@
     <t>Database</t>
   </si>
   <si>
-    <t>Chuyển schema MySQL → SQL Server (ENUM→CHECK, AUTO_INCREMENT→IDENTITY)</t>
+    <t>Chuyển schema MySQL → PostgreSQL (giữ ENUM type, AUTO_INCREMENT→GENERATED ALWAYS AS IDENTITY)</t>
   </si>
   <si>
     <t>1d</t>
@@ -103,7 +103,7 @@
     <t>Giữ nguyên tên bảng/cột để đỡ đổi logic</t>
   </si>
   <si>
-    <t>Cấu hình Dapper + connection factory + stored procedure mẫu</t>
+    <t>Cấu hình psycopg 3 + connection pool + stored procedure mẫu</t>
   </si>
   <si>
     <t>Auth</t>
@@ -139,7 +139,7 @@
     <t>Swagger/OpenAPI setup</t>
   </si>
   <si>
-    <t>Docker Compose khung sườn (api + sqlserver)</t>
+    <t>Docker Compose khung sườn (api + postgres)</t>
   </si>
   <si>
     <t>Should</t>
@@ -334,7 +334,7 @@
     <t>Xuất file</t>
   </si>
   <si>
-    <t>API xuất PDF hóa đơn/báo cáo bằng QuestPDF</t>
+    <t>API xuất PDF hóa đơn/báo cáo bằng ReportLab</t>
   </si>
   <si>
     <t>Tái dùng layout hóa đơn cũ</t>
@@ -343,7 +343,7 @@
     <t>Job nền</t>
   </si>
   <si>
-    <t>Hàng đợi tác vụ (Hangfire) cho gửi mail &amp; xuất báo cáo lớn</t>
+    <t>Hàng đợi tác vụ (Celery) cho gửi mail &amp; xuất báo cáo lớn</t>
   </si>
   <si>
     <t>Chất lượng</t>
@@ -361,7 +361,7 @@
     <t>Chống SQLi/XSS/CSRF, rate limit, CORS</t>
   </si>
   <si>
-    <t>Health check endpoint + logging có cấu trúc (Serilog)</t>
+    <t>Health check endpoint + logging có cấu trúc (structlog)</t>
   </si>
   <si>
     <t>Triển khai</t>
@@ -445,13 +445,13 @@
     <t>Chỉ bán online (không bán tại quầy/POS)</t>
   </si>
   <si>
-    <t>Tách rời Backend (ASP.NET Core Web API + Dapper + SQL Server) và Frontend (AngularJS SPA gọi API qua JWT), khác với project cũ vốn dùng EJS render phía server</t>
+    <t>Tách rời Backend (FastAPI + psycopg 3 + PostgreSQL) và Frontend (AngularJS SPA gọi API qua JWT), khác với project cũ vốn dùng EJS render phía server</t>
   </si>
   <si>
     <t>Stack</t>
   </si>
   <si>
-    <t>.NET 8 (ASP.NET Core) + Dapper + SQL Server + AngularJS + Redis + Docker Compose</t>
+    <t>FastAPI (Python 3.12) + psycopg 3 + PostgreSQL + AngularJS + Redis + Docker Compose</t>
   </si>
   <si>
     <t>Số công việc theo lớp</t>
